--- a/data/Survey_Data.xlsx
+++ b/data/Survey_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ktaylor3/Downloads/MCB536/tfcb-homework01/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BA02ADF1-4EAC-434D-BEB7-C2D5043B767D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C6374DE8-CA0C-F341-AA45-A175C71668EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5100" yWindow="1160" windowWidth="23620" windowHeight="16660" xr2:uid="{C8B4A630-4EA5-3947-8D43-2811E9A6422C}"/>
   </bookViews>
@@ -53,12 +53,6 @@
     <t>Species</t>
   </si>
   <si>
-    <t>Field Season</t>
-  </si>
-  <si>
-    <t>Weight (g)</t>
-  </si>
-  <si>
     <t>F</t>
   </si>
   <si>
@@ -69,9 +63,6 @@
   </si>
   <si>
     <t>DO</t>
-  </si>
-  <si>
-    <t>Scale calibrated</t>
   </si>
   <si>
     <t>DS</t>
@@ -90,6 +81,15 @@
   </si>
   <si>
     <t>OL</t>
+  </si>
+  <si>
+    <t>Weight_in_g</t>
+  </si>
+  <si>
+    <t>Scale_calibrated</t>
+  </si>
+  <si>
+    <t>Field_Season</t>
   </si>
 </sst>
 </file>
@@ -499,16 +499,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -519,16 +519,16 @@
         <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E2" s="1" t="b">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G2">
         <v>2013</v>
@@ -542,7 +542,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D3" s="1">
         <v>33</v>
@@ -551,7 +551,7 @@
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G3">
         <v>2013</v>
@@ -565,16 +565,16 @@
         <v>3</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E4" s="1" t="b">
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G4">
         <v>2013</v>
@@ -588,16 +588,16 @@
         <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E5" s="1" t="b">
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G5">
         <v>2013</v>
@@ -611,7 +611,7 @@
         <v>3</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D6" s="1">
         <v>40</v>
@@ -620,7 +620,7 @@
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G6">
         <v>2013</v>
@@ -634,7 +634,7 @@
         <v>7</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D7" s="1">
         <v>48</v>
@@ -643,7 +643,7 @@
         <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G7">
         <v>2013</v>
@@ -657,7 +657,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D8" s="1">
         <v>29</v>
@@ -666,7 +666,7 @@
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G8">
         <v>2013</v>
@@ -680,7 +680,7 @@
         <v>6</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D9" s="1">
         <v>37</v>
@@ -689,7 +689,7 @@
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G9">
         <v>2013</v>
@@ -703,7 +703,7 @@
         <v>8</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D10" s="1">
         <v>52</v>
@@ -712,7 +712,7 @@
         <v>1</v>
       </c>
       <c r="F10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G10">
         <v>2013</v>
@@ -726,7 +726,7 @@
         <v>3</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D11" s="1">
         <v>33</v>
@@ -735,7 +735,7 @@
         <v>1</v>
       </c>
       <c r="F11" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G11">
         <v>2013</v>
@@ -749,7 +749,7 @@
         <v>3</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D12" s="1">
         <v>50</v>
@@ -758,7 +758,7 @@
         <v>1</v>
       </c>
       <c r="F12" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G12">
         <v>2013</v>
@@ -772,7 +772,7 @@
         <v>9</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D13" s="1">
         <v>40</v>
@@ -781,7 +781,7 @@
         <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G13">
         <v>2013</v>
@@ -795,7 +795,7 @@
         <v>1</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D14" s="1">
         <v>45</v>
@@ -804,7 +804,7 @@
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G14">
         <v>2013</v>
@@ -818,7 +818,7 @@
         <v>8</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D15" s="1">
         <v>41</v>
@@ -827,7 +827,7 @@
         <v>1</v>
       </c>
       <c r="F15" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G15">
         <v>2013</v>
@@ -841,7 +841,7 @@
         <v>9</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D16" s="1">
         <v>117</v>
@@ -850,7 +850,7 @@
         <v>1</v>
       </c>
       <c r="F16" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G16">
         <v>2013</v>
@@ -864,7 +864,7 @@
         <v>11</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D17" s="1">
         <v>126</v>
@@ -873,7 +873,7 @@
         <v>1</v>
       </c>
       <c r="F17" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G17">
         <v>2013</v>
@@ -887,7 +887,7 @@
         <v>17</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D18" s="1">
         <v>132</v>
@@ -896,7 +896,7 @@
         <v>0</v>
       </c>
       <c r="F18" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G18">
         <v>2013</v>
@@ -910,7 +910,7 @@
         <v>14</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D19" s="1">
         <v>113</v>
@@ -919,7 +919,7 @@
         <v>0</v>
       </c>
       <c r="F19" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G19">
         <v>2013</v>
@@ -933,7 +933,7 @@
         <v>11</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D20" s="1">
         <v>122</v>
@@ -942,7 +942,7 @@
         <v>1</v>
       </c>
       <c r="F20" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G20">
         <v>2013</v>
@@ -956,7 +956,7 @@
         <v>4</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D21" s="1">
         <v>107</v>
@@ -965,7 +965,7 @@
         <v>1</v>
       </c>
       <c r="F21" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G21">
         <v>2013</v>
@@ -979,7 +979,7 @@
         <v>4</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D22" s="1">
         <v>115</v>
@@ -988,7 +988,7 @@
         <v>1</v>
       </c>
       <c r="F22" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G22">
         <v>2013</v>
@@ -1002,7 +1002,7 @@
         <v>1</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D23" s="1">
         <v>40</v>
@@ -1011,7 +1011,7 @@
         <v>1</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G23">
         <v>2014</v>
@@ -1025,7 +1025,7 @@
         <v>1</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D24" s="1">
         <v>36</v>
@@ -1034,7 +1034,7 @@
         <v>1</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G24">
         <v>2014</v>
@@ -1048,7 +1048,7 @@
         <v>1</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D25" s="1">
         <v>51</v>
@@ -1057,7 +1057,7 @@
         <v>1</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G25">
         <v>2014</v>
@@ -1071,7 +1071,7 @@
         <v>1</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D26" s="1">
         <v>44</v>
@@ -1080,7 +1080,7 @@
         <v>1</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G26">
         <v>2014</v>
@@ -1094,7 +1094,7 @@
         <v>1</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D27" s="1">
         <v>146</v>
@@ -1103,7 +1103,7 @@
         <v>1</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G27">
         <v>2014</v>
@@ -1117,16 +1117,16 @@
         <v>2</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E28" s="1" t="b">
         <v>1</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G28">
         <v>2014</v>
@@ -1140,7 +1140,7 @@
         <v>2</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D29" s="1">
         <v>44</v>
@@ -1149,7 +1149,7 @@
         <v>1</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G29">
         <v>2014</v>
@@ -1163,7 +1163,7 @@
         <v>2</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D30" s="1">
         <v>7</v>
@@ -1172,7 +1172,7 @@
         <v>1</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G30">
         <v>2014</v>
@@ -1186,7 +1186,7 @@
         <v>2</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D31" s="1">
         <v>45</v>
@@ -1195,7 +1195,7 @@
         <v>1</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G31">
         <v>2014</v>
@@ -1209,16 +1209,16 @@
         <v>2</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E32" s="1" t="b">
         <v>1</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G32">
         <v>2014</v>
@@ -1232,7 +1232,7 @@
         <v>2</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D33" s="1">
         <v>157</v>
@@ -1241,7 +1241,7 @@
         <v>0</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G33">
         <v>2014</v>
@@ -1255,16 +1255,16 @@
         <v>2</v>
       </c>
       <c r="C34" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E34" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F34" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E34" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="G34">
         <v>2014</v>
@@ -1278,7 +1278,7 @@
         <v>2</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D35" s="1">
         <v>218</v>
@@ -1287,7 +1287,7 @@
         <v>0</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G35">
         <v>2014</v>
@@ -1301,7 +1301,7 @@
         <v>2</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D36" s="1">
         <v>7</v>
@@ -1310,7 +1310,7 @@
         <v>1</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G36">
         <v>2014</v>
@@ -1324,7 +1324,7 @@
         <v>2</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D37" s="1">
         <v>52</v>
@@ -1333,7 +1333,7 @@
         <v>1</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G37">
         <v>2014</v>
@@ -1347,7 +1347,7 @@
         <v>3</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D38" s="1">
         <v>8</v>
@@ -1356,7 +1356,7 @@
         <v>1</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G38">
         <v>2014</v>
@@ -1370,16 +1370,16 @@
         <v>3</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E39" s="1" t="b">
         <v>1</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G39">
         <v>2014</v>
@@ -1393,16 +1393,16 @@
         <v>3</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E40" s="1" t="b">
         <v>1</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G40">
         <v>2014</v>
@@ -1416,7 +1416,7 @@
         <v>3</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D41" s="1">
         <v>182</v>
@@ -1425,7 +1425,7 @@
         <v>1</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G41">
         <v>2014</v>
@@ -1439,7 +1439,7 @@
         <v>3</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D42" s="1">
         <v>29</v>
@@ -1448,7 +1448,7 @@
         <v>1</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G42">
         <v>2014</v>
@@ -1462,7 +1462,7 @@
         <v>3</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D43" s="1">
         <v>115</v>
@@ -1471,7 +1471,7 @@
         <v>1</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G43">
         <v>2014</v>
@@ -1485,7 +1485,7 @@
         <v>3</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D44" s="1">
         <v>190</v>
@@ -1494,7 +1494,7 @@
         <v>1</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G44">
         <v>2014</v>
@@ -1508,7 +1508,7 @@
         <v>4</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D45" s="1">
         <v>37</v>
@@ -1517,7 +1517,7 @@
         <v>1</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G45">
         <v>2014</v>
@@ -1531,16 +1531,16 @@
         <v>4</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E46" s="1" t="b">
         <v>1</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G46">
         <v>2014</v>
@@ -1554,7 +1554,7 @@
         <v>4</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D47" s="1">
         <v>48</v>
@@ -1563,7 +1563,7 @@
         <v>1</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G47">
         <v>2014</v>
@@ -1577,7 +1577,7 @@
         <v>4</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D48" s="1">
         <v>52</v>
@@ -1586,7 +1586,7 @@
         <v>1</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G48">
         <v>2014</v>
@@ -1600,7 +1600,7 @@
         <v>4</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D49" s="1">
         <v>35</v>
@@ -1609,7 +1609,7 @@
         <v>1</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G49">
         <v>2014</v>
